--- a/Nhom06_XayDungHeThongBanQuanAo.xlsx
+++ b/Nhom06_XayDungHeThongBanQuanAo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GitHub\DACNMP-Nhom06\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UpGit\DACNMP-Nhom06-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837A0B45-9EBD-4A50-9B8E-D4CE086FA90E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1162FE8F-DB1F-48A0-B676-38E44CA87D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Information" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="99">
   <si>
     <t>I. Requirements</t>
   </si>
@@ -105,21 +105,6 @@
     <t>sprint 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Vẽ Usecase/Xác định Usecase </t>
-  </si>
-  <si>
-    <t>Đặc tả Usecase và vẽ Activity</t>
-  </si>
-  <si>
-    <t>Sơ đồ ERD</t>
-  </si>
-  <si>
-    <t>Vẽ Sequence</t>
-  </si>
-  <si>
-    <t>Vẽ State chart</t>
-  </si>
-  <si>
     <t>E-COMMERCE PROJECT - SPRINT BACKLOG</t>
   </si>
   <si>
@@ -175,9 +160,6 @@
   </si>
   <si>
     <t>công</t>
-  </si>
-  <si>
-    <t>Actor: là khách hàng tôi muốn</t>
   </si>
   <si>
     <t>Đăng nhập</t>
@@ -252,41 +234,164 @@
 Báo cáo quản trị | Tổng hợp doanh thu, tồn kho, lợi nhuận</t>
   </si>
   <si>
-    <t>Actor: là admin tôi muốn</t>
-  </si>
-  <si>
-    <t>Thêm xóa Sửa sản phẩm</t>
-  </si>
-  <si>
-    <t>Thêm danh mục sản phẩm</t>
-  </si>
-  <si>
     <t>Thanh toán</t>
   </si>
   <si>
     <t>tìm kiếm sản phẩm</t>
   </si>
   <si>
-    <t>chỉnh sửa trạng thái đơn hàng</t>
-  </si>
-  <si>
-    <t>đăng nhập tài khoản admin</t>
-  </si>
-  <si>
-    <t>đăng xuất tài khoản admin</t>
-  </si>
-  <si>
-    <t>thanh toán</t>
-  </si>
-  <si>
     <t>Đạt</t>
+  </si>
+  <si>
+    <t>xem trang chủ</t>
+  </si>
+  <si>
+    <t>chăm sóc khách hàng</t>
+  </si>
+  <si>
+    <t>quên mật khẩu</t>
+  </si>
+  <si>
+    <t>quản lý khuyến mãi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xem danh sách sản phẩm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">đăng ký tài khoản </t>
+  </si>
+  <si>
+    <t>đăng nhập</t>
+  </si>
+  <si>
+    <t>đăng xuất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quên mật khẩu </t>
+  </si>
+  <si>
+    <t>xem chi tiết sản phẩm</t>
+  </si>
+  <si>
+    <t>quản lý thông tin ( thêm xóa sửa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thanh toán trực tuyến </t>
+  </si>
+  <si>
+    <t xml:space="preserve">tìm kiếm và lọc sản phẩm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">quản lý khuyến mãi </t>
+  </si>
+  <si>
+    <t>quản lý sản phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quản lý nhân viên </t>
+  </si>
+  <si>
+    <t>xem lịch sử đặt hàng</t>
+  </si>
+  <si>
+    <t>xem thông tin khách hàng</t>
+  </si>
+  <si>
+    <t>quản lý chi nhánh</t>
+  </si>
+  <si>
+    <t>đặt hàng</t>
+  </si>
+  <si>
+    <t>quản lý khách hàng</t>
+  </si>
+  <si>
+    <t>gửi báo cáo lỗi cho quản lý</t>
+  </si>
+  <si>
+    <t>quản lý đơn hàng</t>
+  </si>
+  <si>
+    <t>xem trạng thái đơn hàng</t>
+  </si>
+  <si>
+    <t>quản lý trạng thái đơn hàng</t>
+  </si>
+  <si>
+    <t>nhận thông báo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xem hình thức thanh toán </t>
+  </si>
+  <si>
+    <t>thống kê</t>
+  </si>
+  <si>
+    <t>quản lý đơn hàng( đăng ký,sửa,hủy)(nhân viên)</t>
+  </si>
+  <si>
+    <t>thêm thông báo</t>
+  </si>
+  <si>
+    <t>xem lịch sử đặt hàng(admin)</t>
+  </si>
+  <si>
+    <t>quản lý ca làm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thành </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phan </t>
+  </si>
+  <si>
+    <t>tìm  kiếm và lọc sản phẩm</t>
+  </si>
+  <si>
+    <t>đăng ký sản phẩm</t>
+  </si>
+  <si>
+    <t>đăng ký tài khoản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đăng nhập </t>
+  </si>
+  <si>
+    <t>quản lý mã khuyến mãi</t>
+  </si>
+  <si>
+    <t>quản lý thông tin(thêm xóa sửa thông tin cá nhân)</t>
+  </si>
+  <si>
+    <t>xem trang thái đơn hàng</t>
+  </si>
+  <si>
+    <t>thanh toán trực tuyến</t>
+  </si>
+  <si>
+    <t>xem hình thức thanh toán</t>
+  </si>
+  <si>
+    <t>quản lý đơn hàng(xem,hủy)</t>
+  </si>
+  <si>
+    <t>Quản lý trạng thái đơn hàng</t>
+  </si>
+  <si>
+    <t>quản lý khuyến mãi(thêm xóa sửa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">` </t>
+  </si>
+  <si>
+    <t>vv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -327,12 +432,6 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -582,44 +681,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -757,11 +818,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -784,85 +897,91 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -870,39 +989,40 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1134,25 +1254,25 @@
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60"/>
+      <c r="A3" s="67" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="68"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
@@ -1161,23 +1281,23 @@
       <c r="W3" s="3"/>
     </row>
     <row r="4" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="68"/>
+      <c r="Q4" s="68"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
@@ -1186,23 +1306,23 @@
       <c r="W4" s="3"/>
     </row>
     <row r="5" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
-      <c r="P5" s="60"/>
-      <c r="Q5" s="60"/>
+      <c r="A5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
@@ -1211,23 +1331,23 @@
       <c r="W5" s="3"/>
     </row>
     <row r="6" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="60"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="60"/>
-      <c r="Q6" s="60"/>
+      <c r="A6" s="68"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="68"/>
+      <c r="Q6" s="68"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
@@ -1236,23 +1356,23 @@
       <c r="W6" s="3"/>
     </row>
     <row r="7" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" s="60"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
+      <c r="A7" s="68"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="68"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="68"/>
+      <c r="Q7" s="68"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
@@ -1261,23 +1381,23 @@
       <c r="W7" s="3"/>
     </row>
     <row r="8" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="60"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
-      <c r="N8" s="60"/>
-      <c r="O8" s="60"/>
-      <c r="P8" s="60"/>
-      <c r="Q8" s="60"/>
+      <c r="A8" s="68"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="68"/>
+      <c r="Q8" s="68"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -1286,23 +1406,23 @@
       <c r="W8" s="3"/>
     </row>
     <row r="9" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="60"/>
-      <c r="K9" s="60"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="60"/>
-      <c r="Q9" s="60"/>
+      <c r="A9" s="68"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="68"/>
+      <c r="N9" s="68"/>
+      <c r="O9" s="68"/>
+      <c r="P9" s="68"/>
+      <c r="Q9" s="68"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
@@ -1311,23 +1431,23 @@
       <c r="W9" s="3"/>
     </row>
     <row r="10" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="60"/>
-      <c r="N10" s="60"/>
-      <c r="O10" s="60"/>
-      <c r="P10" s="60"/>
-      <c r="Q10" s="60"/>
+      <c r="A10" s="68"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="68"/>
+      <c r="Q10" s="68"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
@@ -1336,23 +1456,23 @@
       <c r="W10" s="3"/>
     </row>
     <row r="11" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A11" s="60"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="60"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="60"/>
-      <c r="O11" s="60"/>
-      <c r="P11" s="60"/>
-      <c r="Q11" s="60"/>
+      <c r="A11" s="68"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="68"/>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="68"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="68"/>
+      <c r="Q11" s="68"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
@@ -1361,23 +1481,23 @@
       <c r="W11" s="3"/>
     </row>
     <row r="12" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A12" s="60"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="60"/>
-      <c r="J12" s="60"/>
-      <c r="K12" s="60"/>
-      <c r="L12" s="60"/>
-      <c r="M12" s="60"/>
-      <c r="N12" s="60"/>
-      <c r="O12" s="60"/>
-      <c r="P12" s="60"/>
-      <c r="Q12" s="60"/>
+      <c r="A12" s="68"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="68"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="68"/>
+      <c r="K12" s="68"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="68"/>
+      <c r="P12" s="68"/>
+      <c r="Q12" s="68"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
@@ -1386,23 +1506,23 @@
       <c r="W12" s="3"/>
     </row>
     <row r="13" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A13" s="60"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
-      <c r="N13" s="60"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="60"/>
-      <c r="Q13" s="60"/>
+      <c r="A13" s="68"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="68"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="68"/>
+      <c r="Q13" s="68"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
@@ -1411,23 +1531,23 @@
       <c r="W13" s="3"/>
     </row>
     <row r="14" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A14" s="60"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="60"/>
-      <c r="N14" s="60"/>
-      <c r="O14" s="60"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="60"/>
+      <c r="A14" s="68"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="68"/>
+      <c r="Q14" s="68"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
@@ -1436,23 +1556,23 @@
       <c r="W14" s="3"/>
     </row>
     <row r="15" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A15" s="60"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="60"/>
+      <c r="A15" s="68"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="68"/>
+      <c r="Q15" s="68"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
@@ -1461,23 +1581,23 @@
       <c r="W15" s="3"/>
     </row>
     <row r="16" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A16" s="60"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="60"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="60"/>
+      <c r="A16" s="68"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="68"/>
+      <c r="M16" s="68"/>
+      <c r="N16" s="68"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="68"/>
+      <c r="Q16" s="68"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
@@ -1486,23 +1606,23 @@
       <c r="W16" s="3"/>
     </row>
     <row r="17" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="60"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="60"/>
-      <c r="M17" s="60"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="60"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="60"/>
+      <c r="A17" s="68"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="68"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="68"/>
+      <c r="Q17" s="68"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
@@ -1511,23 +1631,23 @@
       <c r="W17" s="3"/>
     </row>
     <row r="18" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="60"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="60"/>
-      <c r="M18" s="60"/>
-      <c r="N18" s="60"/>
-      <c r="O18" s="60"/>
-      <c r="P18" s="60"/>
-      <c r="Q18" s="60"/>
+      <c r="A18" s="68"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="68"/>
+      <c r="Q18" s="68"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
@@ -1536,23 +1656,23 @@
       <c r="W18" s="3"/>
     </row>
     <row r="19" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="60"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="60"/>
-      <c r="P19" s="60"/>
-      <c r="Q19" s="60"/>
+      <c r="A19" s="68"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="68"/>
+      <c r="P19" s="68"/>
+      <c r="Q19" s="68"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
@@ -1561,23 +1681,23 @@
       <c r="W19" s="3"/>
     </row>
     <row r="20" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A20" s="60"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="60"/>
-      <c r="M20" s="60"/>
-      <c r="N20" s="60"/>
-      <c r="O20" s="60"/>
-      <c r="P20" s="60"/>
-      <c r="Q20" s="60"/>
+      <c r="A20" s="68"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="68"/>
+      <c r="P20" s="68"/>
+      <c r="Q20" s="68"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
@@ -1586,23 +1706,23 @@
       <c r="W20" s="3"/>
     </row>
     <row r="21" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A21" s="60"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="60"/>
-      <c r="M21" s="60"/>
-      <c r="N21" s="60"/>
-      <c r="O21" s="60"/>
-      <c r="P21" s="60"/>
-      <c r="Q21" s="60"/>
+      <c r="A21" s="68"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="68"/>
+      <c r="Q21" s="68"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
@@ -1611,23 +1731,23 @@
       <c r="W21" s="3"/>
     </row>
     <row r="22" spans="1:23" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="60"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="60"/>
-      <c r="M22" s="60"/>
-      <c r="N22" s="60"/>
-      <c r="O22" s="60"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
+      <c r="A22" s="68"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="68"/>
+      <c r="Q22" s="68"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
@@ -3500,14 +3620,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4659,319 +4779,558 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G995"/>
+  <dimension ref="A1:L1004"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="26" customWidth="1"/>
-    <col min="2" max="2" width="67.21875" style="26" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" style="26" customWidth="1"/>
-    <col min="4" max="26" width="8.88671875" style="26" customWidth="1"/>
-    <col min="27" max="16384" width="12.6640625" style="26"/>
+    <col min="1" max="1" width="10" style="24" customWidth="1"/>
+    <col min="2" max="2" width="67.21875" style="24" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" style="24" customWidth="1"/>
+    <col min="4" max="26" width="8.88671875" style="24" customWidth="1"/>
+    <col min="27" max="16384" width="12.6640625" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="25" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="28"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="26"/>
     </row>
     <row r="3" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="30" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="34"/>
+    <row r="4" spans="1:7" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="31"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="32"/>
     </row>
     <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="35"/>
-      <c r="B5" s="36" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="37"/>
+      <c r="C5" s="66"/>
     </row>
     <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38">
+      <c r="A6" s="60">
         <v>1</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="38">
+        <v>2</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="36">
+        <v>3</v>
+      </c>
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="38">
+        <v>3</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="38">
+        <v>4</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="38">
+        <v>5</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="38">
+        <v>6</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="38">
+        <v>7</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="38">
+        <v>8</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="38">
+        <v>9</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="38">
+        <v>10</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="38">
+        <v>11</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="38">
+        <v>12</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="38">
+        <v>13</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="40"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="42"/>
+    </row>
+    <row r="20" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="43">
+        <v>14</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="43">
+        <v>15</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="43">
+        <v>3</v>
+      </c>
+      <c r="L21" s="24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="43">
+        <v>16</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="43">
+        <v>17</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="43">
+        <v>18</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="43">
+        <v>19</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="43">
+        <v>20</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="43">
+        <v>21</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="43">
         <v>22</v>
       </c>
-      <c r="C6" s="40">
+      <c r="B28" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="36">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41">
+    <row r="29" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="33"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="45"/>
+    </row>
+    <row r="30" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="60">
+        <v>23</v>
+      </c>
+      <c r="B30" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="38">
+        <v>24</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="38">
+        <v>25</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="38">
+        <v>26</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="38">
+        <v>27</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="38">
+        <v>28</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="38">
+        <v>29</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="33"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="45"/>
+    </row>
+    <row r="38" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="60">
+        <v>30</v>
+      </c>
+      <c r="B38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="63">
         <v>2</v>
       </c>
-      <c r="B7" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="40">
+    </row>
+    <row r="39" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="38">
+        <v>31</v>
+      </c>
+      <c r="B39" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="38">
+        <v>32</v>
+      </c>
+      <c r="B40" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="38">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="38">
+        <v>34</v>
+      </c>
+      <c r="B42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+    </row>
+    <row r="44" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="61">
+        <v>35</v>
+      </c>
+      <c r="B44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="62">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="62">
+        <v>37</v>
+      </c>
+      <c r="B46" t="s">
+        <v>66</v>
+      </c>
+      <c r="C46" s="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="62">
+        <v>38</v>
+      </c>
+      <c r="B47" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="62">
+        <v>39</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C48" s="64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="62">
+        <v>40</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="62">
+        <v>41</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" s="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="62">
+        <v>42</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" s="64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="62">
+        <v>43</v>
+      </c>
+      <c r="B52" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C52" s="64">
         <v>1</v>
       </c>
-      <c r="G7" s="42"/>
-    </row>
-    <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43">
-        <v>3</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43">
-        <v>4</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43">
-        <v>5</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="45"/>
-      <c r="B11" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="47"/>
-    </row>
-    <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="48">
-        <v>6</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="48">
-        <v>7</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48">
-        <v>8</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="48">
-        <v>9</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="48">
-        <v>10</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="48">
-        <v>11</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48">
-        <v>12</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48">
-        <v>13</v>
-      </c>
-      <c r="B19" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="40">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="48">
-        <v>14</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="35"/>
-      <c r="B21" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="50"/>
-    </row>
-    <row r="22" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="41">
-        <v>15</v>
-      </c>
-      <c r="B22" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="41">
-        <v>16</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="41">
-        <v>17</v>
-      </c>
-      <c r="B24" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="41">
-        <v>18</v>
-      </c>
-      <c r="B25" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="41">
-        <v>19</v>
-      </c>
-      <c r="B26" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="35"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="50"/>
-    </row>
-    <row r="28" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="41"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="40"/>
-    </row>
-    <row r="29" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="53" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5903,6 +6262,15 @@
     <row r="993" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="994" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="995" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1002" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1003" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1004" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -5911,11 +6279,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J1010"/>
+  <dimension ref="A1:M1015"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="2" max="2" width="35.21875" customWidth="1"/>
     <col min="3" max="3" width="6.109375" customWidth="1"/>
     <col min="4" max="4" width="12.88671875" customWidth="1"/>
     <col min="5" max="6" width="9.44140625" customWidth="1"/>
@@ -5927,18 +6295,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="A1" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
@@ -5952,10 +6320,10 @@
     </row>
     <row r="3" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="12"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="60"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="68"/>
     </row>
     <row r="4" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -5968,25 +6336,25 @@
         <v>20</v>
       </c>
       <c r="D4" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="J4" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5994,7 +6362,7 @@
       <c r="B5" s="5"/>
       <c r="C5" s="5">
         <f>SUM(C7:C11)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -6005,31 +6373,31 @@
       <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="69" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="A6" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="78"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="80"/>
     </row>
     <row r="7" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="A7" s="14">
         <v>1</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="5">
-        <v>2</v>
+      <c r="B7" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="15">
+        <v>3</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E7" s="7">
         <v>45916</v>
@@ -6037,23 +6405,29 @@
       <c r="F7" s="7">
         <v>45921</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="5"/>
+      <c r="G7" s="7">
+        <v>45917</v>
+      </c>
+      <c r="H7" s="7">
+        <v>45921</v>
+      </c>
+      <c r="I7" s="15">
+        <v>3</v>
+      </c>
       <c r="J7" s="5"/>
     </row>
     <row r="8" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="14">
         <v>2</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="5">
-        <v>2</v>
+      <c r="B8" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="15">
+        <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E8" s="7">
         <v>45916</v>
@@ -6061,23 +6435,29 @@
       <c r="F8" s="7">
         <v>45921</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="5"/>
+      <c r="G8" s="7">
+        <v>45917</v>
+      </c>
+      <c r="H8" s="7">
+        <v>45921</v>
+      </c>
+      <c r="I8" s="15">
+        <v>1</v>
+      </c>
       <c r="J8" s="5"/>
     </row>
     <row r="9" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="A9" s="14">
         <v>3</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2</v>
+      <c r="B9" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="15">
+        <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E9" s="7">
         <v>45916</v>
@@ -6085,23 +6465,29 @@
       <c r="F9" s="7">
         <v>45921</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="5"/>
+      <c r="G9" s="7">
+        <v>45917</v>
+      </c>
+      <c r="H9" s="7">
+        <v>45921</v>
+      </c>
+      <c r="I9" s="15">
+        <v>1</v>
+      </c>
       <c r="J9" s="5"/>
     </row>
     <row r="10" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="A10" s="14">
         <v>4</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2</v>
+      <c r="B10" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="15">
+        <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E10" s="7">
         <v>45916</v>
@@ -6109,23 +6495,29 @@
       <c r="F10" s="7">
         <v>45921</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="5"/>
+      <c r="G10" s="7">
+        <v>45917</v>
+      </c>
+      <c r="H10" s="7">
+        <v>45921</v>
+      </c>
+      <c r="I10" s="15">
+        <v>1</v>
+      </c>
       <c r="J10" s="5"/>
     </row>
     <row r="11" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="A11" s="14">
         <v>5</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="B11" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="15">
         <v>2</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E11" s="7">
         <v>45916</v>
@@ -6133,46 +6525,88 @@
       <c r="F11" s="7">
         <v>45921</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="5"/>
+      <c r="G11" s="7">
+        <v>45917</v>
+      </c>
+      <c r="H11" s="7">
+        <v>45921</v>
+      </c>
+      <c r="I11" s="15">
+        <v>2</v>
+      </c>
       <c r="J11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="5"/>
+      <c r="A12" s="14">
+        <v>6</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="15">
+        <v>2</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="7">
+        <v>45916</v>
+      </c>
+      <c r="F12" s="7">
+        <v>45921</v>
+      </c>
+      <c r="G12" s="7">
+        <v>45917</v>
+      </c>
+      <c r="H12" s="7">
+        <v>45921</v>
+      </c>
+      <c r="I12" s="15">
+        <v>2</v>
+      </c>
       <c r="J12" s="5"/>
     </row>
     <row r="13" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="5"/>
+      <c r="A13" s="14">
+        <v>7</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="15">
+        <v>2</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="7">
+        <v>45916</v>
+      </c>
+      <c r="F13" s="7">
+        <v>45921</v>
+      </c>
+      <c r="G13" s="7">
+        <v>45917</v>
+      </c>
+      <c r="H13" s="7">
+        <v>45921</v>
+      </c>
+      <c r="I13" s="15">
+        <v>2</v>
+      </c>
       <c r="J13" s="5"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="74"/>
+      <c r="A14" s="81"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="83"/>
     </row>
     <row r="15" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -6190,387 +6624,788 @@
       <c r="J15" s="5"/>
     </row>
     <row r="16" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="65" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="67"/>
+      <c r="A16" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="75"/>
     </row>
     <row r="17" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
-        <v>6</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="20">
-        <v>2</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>39</v>
+      <c r="A17" s="14">
+        <v>8</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="18">
+        <v>3</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="E17" s="7">
         <v>45924</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="16">
         <v>45934</v>
       </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="5"/>
+      <c r="G17" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H17" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I17" s="18">
+        <v>3</v>
+      </c>
       <c r="J17" s="5"/>
     </row>
     <row r="18" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="16">
-        <v>7</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="20">
-        <v>2</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>36</v>
+      <c r="A18" s="14">
+        <v>9</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="18">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="E18" s="7">
         <v>45924</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="16">
         <v>45934</v>
       </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="5"/>
+      <c r="G18" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H18" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I18" s="18">
+        <v>1</v>
+      </c>
       <c r="J18" s="5"/>
     </row>
     <row r="19" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16">
-        <v>8</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="20">
-        <v>2</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>38</v>
+      <c r="A19" s="14">
+        <v>10</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="18">
+        <v>1</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>33</v>
       </c>
       <c r="E19" s="7">
         <v>45924</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="16">
         <v>45934</v>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="5"/>
+      <c r="G19" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H19" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I19" s="18">
+        <v>1</v>
+      </c>
       <c r="J19" s="5"/>
     </row>
     <row r="20" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
-        <v>9</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="20">
+      <c r="A20" s="14">
+        <v>11</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="18">
         <v>2</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>37</v>
+      <c r="D20" s="15" t="s">
+        <v>32</v>
       </c>
       <c r="E20" s="7">
         <v>45924</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="16">
         <v>45934</v>
       </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="5"/>
+      <c r="G20" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H20" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I20" s="18">
+        <v>2</v>
+      </c>
       <c r="J20" s="5"/>
     </row>
     <row r="21" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
-        <v>10</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="20">
+      <c r="A21" s="14">
+        <v>12</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="18">
         <v>2</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>40</v>
+      <c r="D21" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="E21" s="7">
         <v>45924</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="16">
         <v>45934</v>
       </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="5"/>
+      <c r="G21" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H21" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I21" s="18">
+        <v>2</v>
+      </c>
       <c r="J21" s="5"/>
     </row>
     <row r="22" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16">
-        <v>11</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="20">
+      <c r="A22" s="14">
+        <v>13</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="18">
         <v>2</v>
       </c>
-      <c r="D22" s="19" t="s">
-        <v>45</v>
+      <c r="D22" s="17" t="s">
+        <v>40</v>
       </c>
       <c r="E22" s="7">
         <v>45925</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="16">
         <v>45934</v>
       </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="5"/>
+      <c r="G22" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H22" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I22" s="18">
+        <v>2</v>
+      </c>
       <c r="J22" s="5"/>
     </row>
     <row r="23" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16">
-        <v>12</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="20">
-        <v>1</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>51</v>
+      <c r="A23" s="14">
+        <v>14</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="55">
+        <v>2</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>45</v>
       </c>
       <c r="E23" s="7">
         <v>45925</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="16">
         <v>45934</v>
       </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="5"/>
+      <c r="G23" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H23" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I23" s="55">
+        <v>2</v>
+      </c>
       <c r="J23" s="5"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="62"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="64"/>
+      <c r="A24" s="14">
+        <v>15</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="18">
+        <v>2</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="7">
+        <v>45925</v>
+      </c>
+      <c r="F24" s="16">
+        <v>45934</v>
+      </c>
+      <c r="G24" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H24" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I24" s="18">
+        <v>2</v>
+      </c>
+      <c r="J24" s="53"/>
     </row>
     <row r="25" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5">
-        <f>SUM(C27:C33)</f>
-        <v>13</v>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
+      <c r="A25" s="14">
+        <v>16</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="18">
+        <v>2</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="7">
+        <v>45925</v>
+      </c>
+      <c r="F25" s="16">
+        <v>45934</v>
+      </c>
+      <c r="G25" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H25" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I25" s="18">
+        <v>2</v>
+      </c>
+      <c r="J25" s="53"/>
     </row>
     <row r="26" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="65" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="66"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="67"/>
+      <c r="A26" s="14">
+        <v>17</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="18">
+        <v>2</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="7">
+        <v>45925</v>
+      </c>
+      <c r="F26" s="16">
+        <v>45934</v>
+      </c>
+      <c r="G26" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H26" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I26" s="18">
+        <v>2</v>
+      </c>
+      <c r="J26" s="53"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="53">
-        <v>12</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="20">
-        <v>5</v>
-      </c>
-      <c r="D27" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="54">
+      <c r="A27" s="14">
+        <v>18</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="18">
+        <v>3</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="7">
+        <v>45925</v>
+      </c>
+      <c r="F27" s="16">
+        <v>45934</v>
+      </c>
+      <c r="G27" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H27" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I27" s="18">
+        <v>3</v>
+      </c>
+      <c r="J27" s="53"/>
+    </row>
+    <row r="28" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="14">
+        <v>19</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="18">
+        <v>2</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="7">
+        <v>45925</v>
+      </c>
+      <c r="F28" s="16">
+        <v>45934</v>
+      </c>
+      <c r="G28" s="7">
+        <v>45925</v>
+      </c>
+      <c r="H28" s="16">
+        <v>45935</v>
+      </c>
+      <c r="I28" s="18">
+        <v>2</v>
+      </c>
+      <c r="J28" s="53"/>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="70"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="72"/>
+    </row>
+    <row r="30" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5">
+        <f>SUM(C32:C38)</f>
+        <v>15</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+    </row>
+    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="74"/>
+      <c r="C31" s="74"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="75"/>
+    </row>
+    <row r="32" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="46">
+        <v>20</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="18">
+        <v>2</v>
+      </c>
+      <c r="D32" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="47">
         <v>45939</v>
       </c>
-      <c r="F27" s="54">
+      <c r="F32" s="47">
         <v>45950</v>
       </c>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="17"/>
-    </row>
-    <row r="28" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="53">
-        <v>13</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="20">
+      <c r="G32" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H32" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I32" s="18">
         <v>2</v>
       </c>
-      <c r="D28" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="54">
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="46">
+        <v>21</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="18">
+        <v>3</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="47">
         <v>45940</v>
       </c>
-      <c r="F28" s="54">
+      <c r="F33" s="47">
         <v>45951</v>
       </c>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="17"/>
-    </row>
-    <row r="29" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="53">
-        <v>14</v>
-      </c>
-      <c r="B29" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="20">
+      <c r="G33" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H33" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I33" s="18">
+        <v>3</v>
+      </c>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="46">
+        <v>22</v>
+      </c>
+      <c r="B34" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="18">
         <v>2</v>
       </c>
-      <c r="D29" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="54">
+      <c r="D34" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="47">
         <v>45941</v>
       </c>
-      <c r="F29" s="54">
+      <c r="F34" s="47">
         <v>45952</v>
       </c>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="17"/>
-    </row>
-    <row r="30" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="53">
-        <v>15</v>
-      </c>
-      <c r="B30" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="20">
+      <c r="G34" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H34" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I34" s="18">
         <v>2</v>
       </c>
-      <c r="D30" s="58" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="54">
+      <c r="J34" s="15"/>
+      <c r="M34" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="46">
+        <v>23</v>
+      </c>
+      <c r="B35" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="18">
+        <v>3</v>
+      </c>
+      <c r="D35" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="47">
         <v>45940</v>
       </c>
-      <c r="F30" s="54">
+      <c r="F35" s="47">
         <v>45952</v>
       </c>
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="17"/>
-    </row>
-    <row r="31" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="53">
-        <v>16</v>
-      </c>
-      <c r="B31" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="20">
+      <c r="G35" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H35" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I35" s="18">
+        <v>3</v>
+      </c>
+      <c r="J35" s="15"/>
+    </row>
+    <row r="36" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="46">
+        <v>24</v>
+      </c>
+      <c r="B36" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="18">
         <v>2</v>
       </c>
-      <c r="D31" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" s="54">
+      <c r="D36" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="E36" s="47">
         <v>45940</v>
       </c>
-      <c r="F31" s="54">
+      <c r="F36" s="47">
         <v>45951</v>
       </c>
-      <c r="G31" s="54"/>
-      <c r="H31" s="54"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="17"/>
-    </row>
-    <row r="32" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="53"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="17"/>
-    </row>
-    <row r="33" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="53"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="17"/>
-    </row>
-    <row r="34" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G36" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H36" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I36" s="18">
+        <v>2</v>
+      </c>
+      <c r="J36" s="15"/>
+    </row>
+    <row r="37" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="46">
+        <v>25</v>
+      </c>
+      <c r="B37" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="18">
+        <v>1</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="47">
+        <v>45940</v>
+      </c>
+      <c r="F37" s="47">
+        <v>45951</v>
+      </c>
+      <c r="G37" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H37" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I37" s="18">
+        <v>1</v>
+      </c>
+      <c r="J37" s="15"/>
+    </row>
+    <row r="38" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="46">
+        <v>26</v>
+      </c>
+      <c r="B38" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="55">
+        <v>2</v>
+      </c>
+      <c r="D38" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="47">
+        <v>45940</v>
+      </c>
+      <c r="F38" s="47">
+        <v>45951</v>
+      </c>
+      <c r="G38" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H38" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I38" s="55">
+        <v>2</v>
+      </c>
+      <c r="J38" s="57"/>
+    </row>
+    <row r="39" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="46">
+        <v>27</v>
+      </c>
+      <c r="B39" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="18">
+        <v>1</v>
+      </c>
+      <c r="D39" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="47">
+        <v>45940</v>
+      </c>
+      <c r="F39" s="47">
+        <v>45951</v>
+      </c>
+      <c r="G39" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H39" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I39" s="18">
+        <v>1</v>
+      </c>
+      <c r="J39" s="58"/>
+    </row>
+    <row r="40" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="46">
+        <v>28</v>
+      </c>
+      <c r="B40" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="18">
+        <v>3</v>
+      </c>
+      <c r="D40" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="47">
+        <v>45940</v>
+      </c>
+      <c r="F40" s="47">
+        <v>45951</v>
+      </c>
+      <c r="G40" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H40" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I40" s="18">
+        <v>3</v>
+      </c>
+      <c r="J40" s="58"/>
+    </row>
+    <row r="41" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="46">
+        <v>29</v>
+      </c>
+      <c r="B41" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="18">
+        <v>1</v>
+      </c>
+      <c r="D41" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="47">
+        <v>45940</v>
+      </c>
+      <c r="F41" s="47">
+        <v>45951</v>
+      </c>
+      <c r="G41" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H41" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I41" s="18">
+        <v>1</v>
+      </c>
+      <c r="J41" s="58"/>
+    </row>
+    <row r="42" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="46">
+        <v>30</v>
+      </c>
+      <c r="B42" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="18">
+        <v>1</v>
+      </c>
+      <c r="D42" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" s="47">
+        <v>45940</v>
+      </c>
+      <c r="F42" s="47">
+        <v>45951</v>
+      </c>
+      <c r="G42" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H42" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I42" s="18">
+        <v>1</v>
+      </c>
+      <c r="J42" s="58"/>
+    </row>
+    <row r="43" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="46">
+        <v>31</v>
+      </c>
+      <c r="B43" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="18">
+        <v>2</v>
+      </c>
+      <c r="D43" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="47">
+        <v>45940</v>
+      </c>
+      <c r="F43" s="47">
+        <v>45951</v>
+      </c>
+      <c r="G43" s="47">
+        <v>45940</v>
+      </c>
+      <c r="H43" s="47">
+        <v>45952</v>
+      </c>
+      <c r="I43" s="18">
+        <v>2</v>
+      </c>
+      <c r="J43" s="58"/>
+    </row>
+    <row r="44" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7533,10 +8368,15 @@
     <row r="1008" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1009" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1010" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1011" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1012" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1013" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1014" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1015" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="E3:F3"/>
